--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Nilam Karki Basnet</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9841258917</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9841258917</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -889,10 +887,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.67657</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.67657</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -948,25 +944,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.30774</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.30774</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1062,10 +1054,8 @@
           <t>Nipen Shrestha</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9840093673</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9840093673</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1100,10 +1090,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.68972</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.68972</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1159,25 +1147,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.32863</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.32863</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1273,10 +1257,8 @@
           <t>Nipen Shrestha</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9840093673</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9840093673</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1311,10 +1293,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.68972</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.68972</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1370,25 +1350,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.32863</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.32863</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1437,7 +1413,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1728,7 +1704,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1795,7 +1771,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1862,7 +1838,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -501,35 +501,35 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1390,6 +1390,209 @@
       <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 8:42 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365217</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>yogendra thapa</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>yogendra thapa</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9843286330</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 08:42:10 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>CHB9843286330</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 09:16:31 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 08:42:10 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Fikkal park Khimkumar house - Housing society P93J+8R Kageshwori Manohara 44600, Kathmandu, Nepal, N</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>parbatkatuwal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L24-5</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>23h 25m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -1404,16 +1607,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1441,7 +1644,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1451,7 +1654,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1486,7 +1689,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>4d 3h 32m</t>
+          <t>3d 8h 30m</t>
         </is>
       </c>
     </row>
@@ -1538,337 +1741,445 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>TKT1355718</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Nilam Karki Basnet</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 05:34:53 PM</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>8d 14h 24m</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TKT1364200</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Nipen Shrestha</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>TKT1355718</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Nilam Karki Basnet</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:59:43 AM</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:34:53 PM</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:59:43 AM</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>8d 14h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>TKT1364200</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Nipen Shrestha</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:58:19 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:52:25 AM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:58:19 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>1d 22h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364200</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Nipen Shrestha</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>1d 22h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365217</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>yogendra thapa</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 08:42:10 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 09:16:31 AM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 08:42:10 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>23h 25m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1460,10 +1460,8 @@
           <t>yogendra thapa</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9843286330</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9843286330</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1553,10 +1551,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1567,7 +1563,7 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1616,7 +1612,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2149,7 +2145,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -497,7 +497,7 @@
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -1589,6 +1589,209 @@
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:21 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363387</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Hemchandra</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Hemchandra</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9812298857</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:21:57 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>BRJ9812298857</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:49:53 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:21:57 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.012149</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>2V6P+VH5, National Medical College Rd, Birgunj 44400, Narayani, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>A7-CDB5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>84.886604</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 32m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1843,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1661,7 +1864,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -1726,14 +1929,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1802,14 +2005,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -510,24 +510,24 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="21" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
@@ -1659,10 +1659,8 @@
           <t>Hemchandra</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9812298857</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9812298857</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1697,10 +1695,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.012149</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.012149</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1748,50 +1744,675 @@
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>A7-CDB5</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>84.886604</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>84.88660400000001</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 32m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade  has been updated by Om Neupane</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:33 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>red light issue</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364745</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Rajkumar Waiba</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Rajkumar Waiba</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9845677282</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:33:28 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9845677282</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:28:55 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:33:28 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.640133</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near Sunrise Bank Ltd. Bhaisepati Branch J8R4+62Q, Karyabinayak 44700., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>13:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.304674</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>2d 20h 32m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 4m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:40 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>net tv</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366161</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9863686590</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:47:38 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9863686590</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:14:26 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:40:48 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.68805</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Manohara Restaurant &amp; Party Palace,Bhaktapur Road, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>sameer.nepal11111@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.3649</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>53m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1h 26m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:33 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366221</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>prem ghising</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>prem ghising</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9844283687</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:41:09 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>CHB9844283687</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:00:30 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:41:09 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.726082817119774</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>ktm kageshwori gothatar fikal Chowk , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>tgy6@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L24-6</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.41114807128908</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>40m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (In Progress)</t>
         </is>
       </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade  has been updated by Om Neupane</t>
-        </is>
-      </c>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1806,16 +2427,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1843,7 +2464,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1853,7 +2474,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1864,7 +2485,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -1888,7 +2509,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 8h 30m</t>
+          <t>3d 49m</t>
         </is>
       </c>
     </row>
@@ -1929,14 +2550,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1947,438 +2568,569 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>IPTV Remote damage Issue</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1355718</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Nilam Karki Basnet</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 05:34:53 PM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>8d 14h 24m</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1364200</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Nipen Shrestha</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>1d 22h 5m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364200</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Nipen Shrestha</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>TKT1355718</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Nilam Karki Basnet</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:59:43 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:34:53 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:59:43 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>8d 14h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364200</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Nipen Shrestha</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:58:19 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:52:25 AM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:58:19 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364200</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Nipen Shrestha</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:58:19 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:52:25 AM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:58:19 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>1d 22h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>TKT1365217</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>yogendra thapa</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>IPTV Remote damage Issue</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 09:16:31 AM</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>23h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364745</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Rajkumar Waiba</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:33:28 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:28:55 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:33:28 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>1d 18h 4m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1854,10 +1854,8 @@
           <t>Rajkumar Waiba</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9845677282</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9845677282</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1892,10 +1890,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.640133</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.640133</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1947,25 +1943,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>4,16</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.304674</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.30467400000001</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2061,10 +2053,8 @@
           <t>Samir Nepal</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9863686590</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9863686590</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2099,10 +2089,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.68805</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.68805</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2154,25 +2142,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L10-3</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.3649</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.36490000000001</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : net tv  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2268,10 +2252,8 @@
           <t>prem ghising</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9844283687</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9844283687</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2306,10 +2288,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.726082817119774</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.72608281711977</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2347,10 +2327,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2369,48 +2347,147 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L24-6</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.41114807128908</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.41114807128908</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>40m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>40m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:55 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr"/>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr"/>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2427,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2436,7 +2513,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2464,7 +2541,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2485,7 +2562,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -2597,84 +2674,75 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2754,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -2704,244 +2772,148 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355718</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Nilam Karki Basnet</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 05:34:53 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>8d 14h 24m</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364200</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Nipen Shrestha</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1364200</t>
+          <t>TKT1355718</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Nipen Shrestha</t>
+          <t>Nilam Karki Basnet</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2971,22 +2943,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
+          <t>02 Oct 2026 05:34:53 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -2996,29 +2968,29 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1365217</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>yogendra thapa</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3038,22 +3010,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 09:16:31 AM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -3063,72 +3035,206 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>23h 25m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>TKT1364200</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Nipen Shrestha</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:58:19 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:52:25 AM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:58:19 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>1d 22h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365217</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>yogendra thapa</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 08:42:10 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 09:16:31 AM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 08:42:10 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>23h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>TKT1364745</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Rajkumar Waiba</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 04:28:55 PM</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>1d 18h 4m</t>
         </is>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2493,6 +2493,639 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>net tv</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366161</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9863686590</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9863686590</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:14:26 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.68805</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Manohara Restaurant &amp; Party Palace,Bhaktapur Road, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>sameer.nepal11111@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.3649</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>1h 57m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>net tv</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366161</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9863686590</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9863686590</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:14:26 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.68805</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Manohara Restaurant &amp; Party Palace,Bhaktapur Road, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>sameer.nepal11111@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.3649</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1h 57m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:57 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>net tv</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366161</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9863686590</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9863686590</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:14:26 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.68805</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Manohara Restaurant &amp; Party Palace,Bhaktapur Road, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>sameer.nepal11111@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.3649</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1h 57m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2504,16 +3137,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2541,7 +3174,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2551,7 +3184,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2562,7 +3195,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2586,7 +3219,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 49m</t>
+          <t>1d 22h 14m</t>
         </is>
       </c>
     </row>
@@ -2663,14 +3296,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2804,14 +3437,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3240,6 +3873,207 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366161</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:14:26 AM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>1h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1366161</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:14:26 AM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>1h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366161</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:14:26 AM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>1h 57m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,23 +483,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -515,16 +515,16 @@
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="31" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="21" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
@@ -2560,10 +2560,8 @@
           <t>Samir Nepal</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9863686590</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9863686590</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2598,10 +2596,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.68805</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.68805</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2657,25 +2653,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L10-3</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.3649</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.36490000000001</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : net tv  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2771,10 +2763,8 @@
           <t>Samir Nepal</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9863686590</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9863686590</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2809,10 +2799,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.68805</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.68805</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2868,25 +2856,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L10-3</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.3649</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.36490000000001</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -2982,10 +2966,8 @@
           <t>Samir Nepal</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9863686590</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9863686590</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3020,10 +3002,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.68805</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.68805</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3079,48 +3059,1883 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L10-3</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.3649</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.36490000000001</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1h 57m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS13" s="3" t="inlineStr">
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:35 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>range issue</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364159</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Aarati Malla Thakuri</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Aarati Malla Thakuri</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9849257495</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 11:19:34 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9849257495</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:29:42 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:35:23 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.66091</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Imadol, Mahalaxmi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>4,6</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.347773</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>2d 15m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 5m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:46 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365912</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Sanju Rajya Laxmi Rana</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Sanju Rajya Laxmi Rana</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9841595469</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:46:03 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9841595469</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:47:34 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:46:03 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.715261</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Near New par Taylor, Gaurighat Marg, Chabahil, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>sanjurt7@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>L13-2</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.347545</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>1h 57m</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>14h 58m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW13" s="3" t="inlineStr">
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:28 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364684</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Bhumi Raj Bhandari</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Bhumi Raj Bhandari</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9865036914</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:28:28 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9865036914</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:42:56 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:28:28 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Near Dhapasi Height Details from Google Maps Q82P+PC8, Dhapasi Marg, Tokha 44600, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>krishibhumi@outlook.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>14:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L15-6</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 45m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:04 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359439</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Milan Sijali</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Milan Sijali</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9818520293</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:04:49 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>CHB9818520293</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:06:45 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:04:49 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>27.717372359536917, 85.34458571343386, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>9818520293@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>07:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L27-2</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 58m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:31 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364527</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Vicky Shahi</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Vicky Shahi</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9841732382</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:28:36 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9801970444</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:28:36 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:31:53 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Tikhedewal Chumlung Kirati Bhawan, , ,</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>bkeeshahi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 3m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 3m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:22 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365285</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Pabita Ale</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Pabita Ale</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9811806755</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:22:40 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>LTP9811806755</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:07:56 AM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:22:40 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Patan Sundhara, Lalitpur, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>09:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L112-6</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 14m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:38 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364817</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Indra Bahadur Roka</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Indra Bahadur Roka</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9869758776</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9869758776</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:38:10 AM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>near by Machchhe Narayan Temple - Hindu temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>9869758776@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>12:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>CDB262</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:37 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364817</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Indra Bahadur Roka</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Indra Bahadur Roka</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9869758776</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9869758776</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:38:10 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>near by Machchhe Narayan Temple - Hindu temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>9869758776@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>12:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB262</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:36 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364249</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Ashish Shrestha</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Ashish Shrestha</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9869088538</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:13:46 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9869088538</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:13:46 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:36:50 AM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.68929</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Satungal Chandragiri , Highvision, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>ashishstha45@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>19:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB415</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.23002</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 23m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 23m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3137,11 +4952,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -3174,7 +4989,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -3184,7 +4999,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -3195,7 +5010,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -3207,7 +5022,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>8h 56m</t>
         </is>
       </c>
     </row>
@@ -3219,7 +5034,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 14m</t>
+          <t>2d 35m</t>
         </is>
       </c>
     </row>
@@ -3260,14 +5075,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -3308,97 +5123,92 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>60.0%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -3410,7 +5220,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -3428,259 +5238,171 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355718</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Nilam Karki Basnet</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 05:34:53 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364200</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Nipen Shrestha</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 5m</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1364200</t>
+          <t>TKT1355718</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Nipen Shrestha</t>
+          <t>Nilam Karki Basnet</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3710,22 +5432,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
+          <t>02 Oct 2026 05:34:53 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -3735,29 +5457,29 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1365217</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>yogendra thapa</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3777,22 +5499,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 09:16:31 AM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3802,29 +5524,29 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>23h 25m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1364745</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Rajkumar Waiba</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3844,22 +5566,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:28:55 PM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -3869,29 +5591,29 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 4m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1365217</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>yogendra thapa</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3906,27 +5628,27 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Case : net tv  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : net tv  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>10 Oct 2026 09:16:31 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -3936,29 +5658,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>23h 25m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1364745</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>Rajkumar Waiba</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3973,27 +5695,27 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>09 Oct 2026 04:28:55 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -4003,7 +5725,7 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>1d 18h 4m</t>
         </is>
       </c>
     </row>
@@ -4040,37 +5762,640 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:14:26 AM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>1h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1366161</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:14:26 AM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:11:41 AM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>1h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366161</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Samir Nepal</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-STB App not working</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 09:14:26 AM</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>1h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365912</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Sanju Rajya Laxmi Rana</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:46:03 AM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:47:34 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:46:03 AM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>14h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364684</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Bhumi Raj Bhandari</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:28:28 AM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:42:56 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:28:28 AM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359439</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Milan Sijali</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:04:49 AM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:06:45 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:04:49 AM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>5d 20h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365285</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Pabita Ale</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:22:40 AM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:07:56 AM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:22:40 AM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364817</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Indra Bahadur Roka</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:38:10 AM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364817</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Indra Bahadur Roka</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:38:10 AM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364249</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Ashish Shrestha</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:13:46 AM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:13:46 AM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:36:50 AM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 23m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 23m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3169,10 +3169,8 @@
           <t>Aarati Malla Thakuri</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9849257495</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9849257495</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3207,10 +3205,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.66091</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.66091</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3258,25 +3254,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>4,6</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.347773</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.347773</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3372,10 +3364,8 @@
           <t>Sanju Rajya Laxmi Rana</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9841595469</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9841595469</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3410,10 +3400,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.715261</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.715261</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3469,25 +3457,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>L13-2</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.347545</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.347545</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3583,10 +3567,8 @@
           <t>Bhumi Raj Bhandari</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9865036914</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9865036914</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3676,10 +3658,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -3690,7 +3670,7 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3786,10 +3766,8 @@
           <t>Milan Sijali</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9818520293</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9818520293</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3879,10 +3857,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -3893,7 +3869,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3989,10 +3965,8 @@
           <t>Vicky Shahi</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9841732382</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9841732382</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4078,10 +4052,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4092,7 +4064,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4188,10 +4160,8 @@
           <t>Pabita Ale</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9811806755</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9811806755</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4281,10 +4251,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4295,7 +4263,7 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4391,10 +4359,8 @@
           <t>Indra Bahadur Roka</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9869758776</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9869758776</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4484,10 +4450,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -4498,7 +4462,7 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4594,10 +4558,8 @@
           <t>Indra Bahadur Roka</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9869758776</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9869758776</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4687,10 +4649,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4701,7 +4661,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4797,10 +4757,8 @@
           <t>Ashish Shrestha</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9869088538</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9869088538</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4835,10 +4793,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.68929</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.68929</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4894,25 +4850,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>CDB415</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.23002</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.23002</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -4961,7 +4913,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5963,7 +5915,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -6030,7 +5982,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -6097,7 +6049,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -6164,7 +6116,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -6231,7 +6183,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -6298,7 +6250,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -6365,7 +6317,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW22"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4893,6 +4893,1037 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:16 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366209</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Niras Rai</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Niras Rai</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9860384667</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:16:35 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>nirasrai_fttx</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:49:43 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:16:35 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.65972</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>: Near Mercy Mission Academy, Kusunti, Lalitpur , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>rai.niraj0499@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.30908</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>2h 26m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:11 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>NETTV issue</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366179</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Kristina Chaudhary</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Kristina Chaudhary</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9851161595</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:11:12 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>CHB9851161595</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:30:28 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:11:12 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Chandol jagati marg , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>L39-8</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>2h 40m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:07 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365609</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Prabin vandari</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Prabin vandari</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9860651851</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:07:56 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>LTP9860651851</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:38:29 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:07:56 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur , Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>Abcd@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>05:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>21h 29m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:03 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>router  replaced</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364835</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Rp.Naan &amp; sekuwa house</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Rp.Naan &amp; sekuwa house</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9813537434</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:03:45 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>BKT9813537434</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:36:04 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:03:45 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Royal Ocean Cafe (ROC) - Restaurant M9F2+9FX Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>9813537434@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>12:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>CDB393</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 27m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:15 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365416</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Mohan Saud</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Mohan Saud</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9848660025</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:51:03 AM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9848660025</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:51:03 AM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:15:50 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.68211</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Kumari club balkhu khaptad restaurant, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>9848660025@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>08:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.297709</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>1d 24m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 24m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4904,16 +5935,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4941,7 +5972,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -4951,7 +5982,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -4962,7 +5993,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -4974,7 +6005,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 56m</t>
+          <t>7h 55m</t>
         </is>
       </c>
     </row>
@@ -4986,7 +6017,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 35m</t>
+          <t>1d 17h 7m</t>
         </is>
       </c>
     </row>
@@ -5027,14 +6058,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -5045,10 +6076,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -5063,14 +6094,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -5153,14 +6184,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -5213,282 +6244,194 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355718</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Nilam Karki Basnet</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 05:34:53 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364200</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Nipen Shrestha</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 5m</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1364200</t>
+          <t>TKT1355718</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Nipen Shrestha</t>
+          <t>Nilam Karki Basnet</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5518,22 +6461,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
+          <t>02 Oct 2026 05:34:53 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5543,29 +6486,29 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1365217</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>yogendra thapa</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -5585,22 +6528,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 09:16:31 AM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -5610,29 +6553,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>23h 25m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1364745</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Rajkumar Waiba</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -5652,22 +6595,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:28:55 PM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -5677,29 +6620,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 4m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1365217</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>yogendra thapa</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5719,22 +6662,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : net tv  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>10 Oct 2026 09:16:31 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -5744,29 +6687,29 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>23h 25m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1364745</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>Rajkumar Waiba</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -5786,22 +6729,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>09 Oct 2026 04:28:55 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -5811,7 +6754,7 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>1d 18h 4m</t>
         </is>
       </c>
     </row>
@@ -5853,7 +6796,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -5885,22 +6828,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1365912</t>
+          <t>TKT1366161</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Sanju Rajya Laxmi Rana</t>
+          <t>Samir Nepal</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -5920,22 +6863,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:47:34 PM</t>
+          <t>11 Oct 2026 09:14:26 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -5945,29 +6888,29 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>14h 58m</t>
+          <t>1h 57m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1364684</t>
+          <t>TKT1366161</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Bhumi Raj Bhandari</t>
+          <t>Samir Nepal</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -5987,22 +6930,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:42:56 PM</t>
+          <t>11 Oct 2026 09:14:26 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -6012,19 +6955,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 45m</t>
+          <t>1h 57m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1359439</t>
+          <t>TKT1365912</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Milan Sijali</t>
+          <t>Sanju Rajya Laxmi Rana</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -6054,22 +6997,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 02:06:45 PM</t>
+          <t>10 Oct 2026 08:47:34 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -6079,19 +7022,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 58m</t>
+          <t>14h 58m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1365285</t>
+          <t>TKT1364684</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Pabita Ale</t>
+          <t>Bhumi Raj Bhandari</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6121,22 +7064,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:07:56 AM</t>
+          <t>09 Oct 2026 03:42:56 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -6146,19 +7089,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 14m</t>
+          <t>1d 19h 45m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1364817</t>
+          <t>TKT1359439</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Indra Bahadur Roka</t>
+          <t>Milan Sijali</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -6173,12 +7116,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -6188,44 +7131,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>05 Oct 2026 02:06:45 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:38:10 AM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>5d 20h 58m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1364817</t>
+          <t>TKT1365285</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Indra Bahadur Roka</t>
+          <t>Pabita Ale</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -6240,12 +7183,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -6255,99 +7198,568 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : router change  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>10 Oct 2026 10:07:56 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:38:10 AM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>1d 1h 14m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
+          <t>TKT1364817</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Indra Bahadur Roka</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:38:10 AM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364817</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Indra Bahadur Roka</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:19:02 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:38:10 AM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
           <t>TKT1364249</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Ashish Shrestha</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>11 Oct 2026 11:36:50 AM</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>2d 1h 23m</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>2d 1h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366209</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Niras Rai</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:16:35 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:49:43 AM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:16:35 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>2h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1366179</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Kristina Chaudhary</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:11:12 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:30:28 AM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:11:12 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>2h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365609</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Prabin vandari</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:07:56 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:38:29 PM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:07:56 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>21h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364835</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Rp.Naan &amp; sekuwa house</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:03:45 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:36:04 PM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:03:45 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>1d 18h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365416</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Mohan Saud</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:51:03 AM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:51:03 AM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:15:50 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>1d 24m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>1d 24m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4960,10 +4960,8 @@
           <t>Niras Rai</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9860384667</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9860384667</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4998,10 +4996,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.65972</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.65972</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5057,25 +5053,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>2,8</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.30908</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.30907999999999</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5171,10 +5163,8 @@
           <t>Kristina Chaudhary</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9851161595</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9851161595</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5264,10 +5254,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
@@ -5278,7 +5266,7 @@
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5374,10 +5362,8 @@
           <t>Prabin vandari</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9860651851</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9860651851</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5467,10 +5453,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -5481,7 +5465,7 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5577,10 +5561,8 @@
           <t>Rp.Naan &amp; sekuwa house</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9813537434</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9813537434</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5670,10 +5652,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
@@ -5684,7 +5664,7 @@
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5780,10 +5760,8 @@
           <t>Mohan Saud</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9848660025</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9848660025</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5818,10 +5796,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.68211</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.68211</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5877,25 +5853,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.297709</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.297709</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5944,7 +5916,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7461,7 +7433,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -7528,7 +7500,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -7595,7 +7567,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -7662,7 +7634,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -7729,7 +7701,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW27"/>
+  <dimension ref="A1:AW32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5896,6 +5896,1061 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>STB red light issue</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366330</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Hari Adhikari</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Hari Adhikari</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9841953935</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46:37 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9801236398</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:10:11 AM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46:37 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>27.730217</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Chandol,NCC ace school (near), Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>9801236398@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L29-6</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>85.339671</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>1h 36m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:44 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365831</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Rajendra magar</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Rajendra magar</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9841938159</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:44:56 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>BKT9841938159</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 07:16:39 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:44:56 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Kaushaltar A1 mart, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>Abcd@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>00:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>L17-2</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>17h 28m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365167</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Niru Gurung</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Niru Gurung</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9818320809</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9823790208</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46:21 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>27.72244</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Big Mart, P7CM+9P9, Nagarjun 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>gurungniru2019@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>CDB548</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>85.28168</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:45 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365167</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Niru Gurung</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Niru Gurung</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9818320809</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9823790208</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46:21 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.72244</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Big Mart, P7CM+9P9, Nagarjun 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>gurungniru2019@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>CDB548</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.28168</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:44 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365633</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Mani Kharel</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Mani Kharel</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9763386761</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:54:06 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9843797992</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:54:06 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:44:39 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.68322</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>M7M5+4MQ, Chandragiri 44600 near by Kathmandu shiksha multiple campus, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>asmitkharel95@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>05:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>CDB574</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.26004</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>21h 50m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>21h 50m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5907,7 +6962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5916,7 +6971,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5944,7 +6999,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -5954,7 +7009,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -5965,7 +7020,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -5977,7 +7032,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 55m</t>
+          <t>9h 27m</t>
         </is>
       </c>
     </row>
@@ -5989,7 +7044,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 7m</t>
+          <t>1d 12h 46m</t>
         </is>
       </c>
     </row>
@@ -6030,14 +7085,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -6048,10 +7103,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -6156,14 +7211,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -6202,10 +7257,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -7735,6 +8790,341 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1366330</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Hari Adhikari</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46:37 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 11:10:11 AM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46:37 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>1h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365831</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Rajendra magar</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:44:56 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 07:16:39 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:44:56 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>17h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365167</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Niru Gurung</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46:21 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365167</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Niru Gurung</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46:21 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365633</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Chandra Mani Kharel</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:54:06 PM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:54:06 PM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:44:39 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>21h 50m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>21h 50m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW32"/>
+  <dimension ref="A1:AW34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="31" customWidth="1" min="33" max="33"/>
+    <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -5963,10 +5963,8 @@
           <t>Hari Adhikari</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9841953935</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9841953935</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6001,10 +5999,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>27.730217</t>
-        </is>
+      <c r="Y28" s="3" t="n">
+        <v>27.730217</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -6060,25 +6056,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>L29-6</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>85.339671</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>85.339671</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -6174,10 +6166,8 @@
           <t>Rajendra magar</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9841938159</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9841938159</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6267,10 +6257,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -6281,7 +6269,7 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6377,10 +6365,8 @@
           <t>Niru Gurung</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9818320809</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9818320809</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6415,10 +6401,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>27.72244</t>
-        </is>
+      <c r="Y30" s="3" t="n">
+        <v>27.72244</v>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
@@ -6456,10 +6440,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH30" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH30" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
@@ -6478,25 +6460,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>CDB548</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>85.28168</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>85.28167999999999</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6592,10 +6570,8 @@
           <t>Niru Gurung</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9818320809</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9818320809</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6630,10 +6606,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.72244</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.72244</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6671,10 +6645,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH31" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH31" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
@@ -6693,25 +6665,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>CDB548</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.28168</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.28167999999999</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6807,10 +6775,8 @@
           <t>Chandra Mani Kharel</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9763386761</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9763386761</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6845,10 +6811,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.68322</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.68322</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6904,50 +6868,352 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>CDB574</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.26004</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.26004</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>21h 50m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>21h 50m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>21h 50m</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>21h 50m</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV32" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 1:00 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="3" t="inlineStr"/>
+      <c r="W33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="inlineStr"/>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="AA33" s="3" t="inlineStr"/>
+      <c r="AB33" s="3" t="inlineStr"/>
+      <c r="AC33" s="3" t="inlineStr"/>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr"/>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr"/>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr"/>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr"/>
+      <c r="AM33" s="3" t="inlineStr"/>
+      <c r="AN33" s="3" t="inlineStr"/>
+      <c r="AO33" s="3" t="inlineStr"/>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:51 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>sbt connection</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363024</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Sundar Regmi</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Sundar Regmi</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9803357149</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:00:02 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803357149</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:22:13 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:00:02 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>ktm tokha chowk, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>regmi8@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Bohora</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>L14-8</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -6962,16 +7228,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6999,7 +7265,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -7020,7 +7286,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -7121,14 +7387,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -7299,18 +7565,18 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7322,210 +7588,166 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355718</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Nilam Karki Basnet</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 05:34:53 PM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>8d 14h 24m</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1364200</t>
+          <t>TKT1355718</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nipen Shrestha</t>
+          <t>Nilam Karki Basnet</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -7555,22 +7777,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
+          <t>02 Oct 2026 05:34:53 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -7580,7 +7802,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7844,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -7654,22 +7876,22 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1365217</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>yogendra thapa</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -7689,22 +7911,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 09:16:31 AM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -7714,19 +7936,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>23h 25m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1364745</t>
+          <t>TKT1365217</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Rajkumar Waiba</t>
+          <t>yogendra thapa</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -7736,7 +7958,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -7756,22 +7978,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:28:55 PM</t>
+          <t>10 Oct 2026 09:16:31 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -7781,29 +8003,29 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 4m</t>
+          <t>23h 25m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1364745</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>Rajkumar Waiba</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -7823,22 +8045,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : net tv  has been updated by Sabin Giri</t>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>09 Oct 2026 04:28:55 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -7848,7 +8070,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>1d 18h 4m</t>
         </is>
       </c>
     </row>
@@ -7890,7 +8112,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -7957,7 +8179,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -7989,22 +8211,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1365912</t>
+          <t>TKT1366161</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Sanju Rajya Laxmi Rana</t>
+          <t>Samir Nepal</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -8024,22 +8246,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:47:34 PM</t>
+          <t>11 Oct 2026 09:14:26 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -8049,19 +8271,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>14h 58m</t>
+          <t>1h 57m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1364684</t>
+          <t>TKT1365912</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Bhumi Raj Bhandari</t>
+          <t>Sanju Rajya Laxmi Rana</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -8091,22 +8313,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:42:56 PM</t>
+          <t>10 Oct 2026 08:47:34 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -8116,19 +8338,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 45m</t>
+          <t>14h 58m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1359439</t>
+          <t>TKT1364684</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Milan Sijali</t>
+          <t>Bhumi Raj Bhandari</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -8158,22 +8380,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 02:06:45 PM</t>
+          <t>09 Oct 2026 03:42:56 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -8183,19 +8405,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 58m</t>
+          <t>1d 19h 45m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1365285</t>
+          <t>TKT1359439</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Pabita Ale</t>
+          <t>Milan Sijali</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -8225,22 +8447,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:07:56 AM</t>
+          <t>05 Oct 2026 02:06:45 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -8250,19 +8472,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 14m</t>
+          <t>5d 20h 58m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1364817</t>
+          <t>TKT1365285</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Indra Bahadur Roka</t>
+          <t>Pabita Ale</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -8277,12 +8499,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -8292,32 +8514,32 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : router change  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>10 Oct 2026 10:07:56 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:38:10 AM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>1d 1h 14m</t>
         </is>
       </c>
     </row>
@@ -8391,12 +8613,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1364249</t>
+          <t>TKT1364817</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Ashish Shrestha</t>
+          <t>Indra Bahadur Roka</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -8426,44 +8648,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:13:46 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:13:46 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:36:50 AM</t>
+          <t>11 Oct 2026 11:38:10 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 23m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 23m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1366209</t>
+          <t>TKT1364249</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Niras Rai</t>
+          <t>Ashish Shrestha</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -8478,12 +8700,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -8493,54 +8715,54 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:16:35 PM</t>
+          <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:49:43 AM</t>
+          <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:16:35 PM</t>
+          <t>11 Oct 2026 11:36:50 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 1h 23m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2h 26m</t>
+          <t>2d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1366179</t>
+          <t>TKT1366209</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Kristina Chaudhary</t>
+          <t>Niras Rai</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -8560,22 +8782,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:11:12 PM</t>
+          <t>11 Oct 2026 12:16:35 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:30:28 AM</t>
+          <t>11 Oct 2026 09:49:43 AM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:11:12 PM</t>
+          <t>11 Oct 2026 12:16:35 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -8585,29 +8807,29 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>2h 26m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1365609</t>
+          <t>TKT1366179</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Prabin vandari</t>
+          <t>Kristina Chaudhary</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -8627,22 +8849,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:07:56 PM</t>
+          <t>11 Oct 2026 12:11:12 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:38:29 PM</t>
+          <t>11 Oct 2026 09:30:28 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:07:56 PM</t>
+          <t>11 Oct 2026 12:11:12 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -8652,29 +8874,29 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>21h 29m</t>
+          <t>2h 40m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1364835</t>
+          <t>TKT1365609</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Rp.Naan &amp; sekuwa house</t>
+          <t>Prabin vandari</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -8694,22 +8916,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:03:45 PM</t>
+          <t>11 Oct 2026 12:07:56 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:36:04 PM</t>
+          <t>10 Oct 2026 02:38:29 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:03:45 PM</t>
+          <t>11 Oct 2026 12:07:56 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -8719,39 +8941,39 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 27m</t>
+          <t>21h 29m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1365416</t>
+          <t>TKT1364835</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Mohan Saud</t>
+          <t>Rp.Naan &amp; sekuwa house</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -8761,111 +8983,111 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:03 AM</t>
+          <t>11 Oct 2026 12:03:45 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:03 AM</t>
+          <t>09 Oct 2026 05:36:04 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:15:50 PM</t>
+          <t>11 Oct 2026 12:03:45 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>1d 24m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1d 24m</t>
+          <t>1d 18h 27m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1366330</t>
+          <t>TKT1365416</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Hari Adhikari</t>
+          <t>Mohan Saud</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:37 PM</t>
+          <t>10 Oct 2026 11:51:03 AM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:10:11 AM</t>
+          <t>10 Oct 2026 11:51:03 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:37 PM</t>
+          <t>11 Oct 2026 12:15:50 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 24m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1h 36m</t>
+          <t>1d 24m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1365831</t>
+          <t>TKT1366330</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Rajendra magar</t>
+          <t>Hari Adhikari</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -8890,27 +9112,27 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:56 PM</t>
+          <t>11 Oct 2026 12:46:37 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 07:16:39 PM</t>
+          <t>11 Oct 2026 11:10:11 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:56 PM</t>
+          <t>11 Oct 2026 12:46:37 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -8920,74 +9142,74 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>17h 28m</t>
+          <t>1h 36m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1365167</t>
+          <t>TKT1365831</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Niru Gurung</t>
+          <t>Rajendra magar</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>11 Oct 2026 12:44:56 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>10 Oct 2026 07:16:39 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:21 PM</t>
+          <t>11 Oct 2026 12:44:56 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>17h 28m</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9246,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -9061,65 +9283,132 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
+          <t>TKT1365167</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Niru Gurung</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46:21 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
           <t>TKT1365633</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Chandra Mani Kharel</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 02:54:06 PM</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 02:54:06 PM</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 12:44:39 PM</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>21h 50m</t>
         </is>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="M54" s="3" t="inlineStr">
         <is>
           <t>21h 50m</t>
         </is>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW34"/>
+  <dimension ref="A1:AW42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -7081,10 +7081,8 @@
           <t>Sundar Regmi</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9803357149</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9803357149</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7156,10 +7154,8 @@
           <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
-      <c r="AH34" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH34" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI34" s="3" t="inlineStr"/>
       <c r="AJ34" s="3" t="inlineStr"/>
@@ -7174,10 +7170,8 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
@@ -7188,32 +7182,1692 @@
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 1:10 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365507</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9824866858</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9824866858</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:10:31 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>27.690688, 85.250552, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>CDB594</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>1d 9m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1d 9m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 1:08 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365422</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Thing</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Thing</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9842748830</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:55:36 AM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9842748830</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:55:36 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:08:28 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.6889698</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Link marg , Kuleshwor, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>babutheeng475@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>08:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.2921143</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 1:07 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365422</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Thing</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Thing</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9842748830</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:55:36 AM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9842748830</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:55:36 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:08:28 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.6889698</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Link marg , Kuleshwor, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>babutheeng475@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>08:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.2921143</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 1:14 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359809</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:55:59 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 06:58:32 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:14:23 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.70175</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>27.655793801439316, 85.34194749764016, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>regmiashutosh3@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr"/>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB091A</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.3341</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 18m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>5d 18h 15m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 1:12 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>no light issue in stb box</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364855</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Achhami</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Achhami</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9808426033</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 08:46:00 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>CHB9808426033</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:48:05 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:12:47 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>OM Shanti Chock - Palace Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>hellosachhami0@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 26m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 24m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 1:11 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366242</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Joshua Pradhan</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Joshua Pradhan</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9842749160</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:11:40 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9842749160</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:08:44 AM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:11:40 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.69337</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Near Kathmandu Pragya Kunja School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>joshuavpradhan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>L28-7</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.34139</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>3d 2h 37m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW34" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>3h 2m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 1:10 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365385</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Sonisha Rijal</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Sonisha Rijal</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9858033808</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:10:04 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9858033808</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:25:14 AM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:10:04 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.67971</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Art of Living Center-Nepal, Shankhmul Yoga Park, Kathmandu M8HM+M86, Kathmandu 44600, Bagmati, Centr</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>08:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.33391</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 44m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 1:08 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358878</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Tanisha giri</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Tanisha giri</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9741716174</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:08:51 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>CHB9741716174</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:51 AM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:08:51 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>New baneswor, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>9741716174@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>12:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr"/>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>6d 4h 59m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -7228,7 +8882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7237,7 +8891,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7265,7 +8919,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -7275,7 +8929,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -7286,7 +8940,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>73.2%</t>
         </is>
       </c>
     </row>
@@ -7298,7 +8952,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 27m</t>
+          <t>9h 33m</t>
         </is>
       </c>
     </row>
@@ -7310,7 +8964,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 12h 46m</t>
+          <t>1d 14h 15m</t>
         </is>
       </c>
     </row>
@@ -7351,14 +9005,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -7369,14 +9023,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -7477,14 +9131,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -7523,14 +9177,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -7542,7 +9196,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -7560,23 +9214,23 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7588,18 +9242,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7611,210 +9265,166 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
       <c r="C26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1355718</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Nilam Karki Basnet</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 05:34:53 PM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>8d 14h 24m</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1364200</t>
+          <t>TKT1355718</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Nipen Shrestha</t>
+          <t>Nilam Karki Basnet</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -7844,22 +9454,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
+          <t>02 Oct 2026 05:34:53 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -7869,7 +9479,7 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
@@ -7911,7 +9521,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -7943,22 +9553,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1365217</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>yogendra thapa</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -7978,22 +9588,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 09:16:31 AM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -8003,19 +9613,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>23h 25m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1364745</t>
+          <t>TKT1365217</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Rajkumar Waiba</t>
+          <t>yogendra thapa</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -8025,7 +9635,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -8045,22 +9655,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:28:55 PM</t>
+          <t>10 Oct 2026 09:16:31 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -8070,29 +9680,29 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 4m</t>
+          <t>23h 25m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1364745</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>Rajkumar Waiba</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -8112,22 +9722,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : net tv  has been updated by Sabin Giri</t>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>09 Oct 2026 04:28:55 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -8137,7 +9747,7 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>1d 18h 4m</t>
         </is>
       </c>
     </row>
@@ -8179,7 +9789,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -8246,7 +9856,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -8278,22 +9888,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1365912</t>
+          <t>TKT1366161</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Sanju Rajya Laxmi Rana</t>
+          <t>Samir Nepal</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -8313,22 +9923,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:47:34 PM</t>
+          <t>11 Oct 2026 09:14:26 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -8338,19 +9948,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>14h 58m</t>
+          <t>1h 57m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1364684</t>
+          <t>TKT1365912</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Bhumi Raj Bhandari</t>
+          <t>Sanju Rajya Laxmi Rana</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -8380,22 +9990,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:42:56 PM</t>
+          <t>10 Oct 2026 08:47:34 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -8405,19 +10015,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 19h 45m</t>
+          <t>14h 58m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1359439</t>
+          <t>TKT1364684</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Milan Sijali</t>
+          <t>Bhumi Raj Bhandari</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -8447,22 +10057,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 02:06:45 PM</t>
+          <t>09 Oct 2026 03:42:56 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -8472,19 +10082,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 58m</t>
+          <t>1d 19h 45m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1365285</t>
+          <t>TKT1359439</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Pabita Ale</t>
+          <t>Milan Sijali</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -8514,22 +10124,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:07:56 AM</t>
+          <t>05 Oct 2026 02:06:45 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -8539,19 +10149,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 14m</t>
+          <t>5d 20h 58m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1364817</t>
+          <t>TKT1365285</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Indra Bahadur Roka</t>
+          <t>Pabita Ale</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -8566,12 +10176,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -8581,32 +10191,32 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : router change  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>10 Oct 2026 10:07:56 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:38:10 AM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>1d 1h 14m</t>
         </is>
       </c>
     </row>
@@ -8680,12 +10290,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1364249</t>
+          <t>TKT1364817</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Ashish Shrestha</t>
+          <t>Indra Bahadur Roka</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -8715,44 +10325,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:13:46 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:13:46 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:36:50 AM</t>
+          <t>11 Oct 2026 11:38:10 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 23m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 23m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1366209</t>
+          <t>TKT1364249</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Niras Rai</t>
+          <t>Ashish Shrestha</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -8767,12 +10377,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -8782,54 +10392,54 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:16:35 PM</t>
+          <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:49:43 AM</t>
+          <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:16:35 PM</t>
+          <t>11 Oct 2026 11:36:50 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 1h 23m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>2h 26m</t>
+          <t>2d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1366179</t>
+          <t>TKT1366209</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Kristina Chaudhary</t>
+          <t>Niras Rai</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -8849,22 +10459,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:11:12 PM</t>
+          <t>11 Oct 2026 12:16:35 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:30:28 AM</t>
+          <t>11 Oct 2026 09:49:43 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:11:12 PM</t>
+          <t>11 Oct 2026 12:16:35 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -8874,29 +10484,29 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>2h 26m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1365609</t>
+          <t>TKT1366179</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Prabin vandari</t>
+          <t>Kristina Chaudhary</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -8916,22 +10526,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:07:56 PM</t>
+          <t>11 Oct 2026 12:11:12 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:38:29 PM</t>
+          <t>11 Oct 2026 09:30:28 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:07:56 PM</t>
+          <t>11 Oct 2026 12:11:12 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -8941,29 +10551,29 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>21h 29m</t>
+          <t>2h 40m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1364835</t>
+          <t>TKT1365609</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Rp.Naan &amp; sekuwa house</t>
+          <t>Prabin vandari</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -8983,22 +10593,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:03:45 PM</t>
+          <t>11 Oct 2026 12:07:56 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:36:04 PM</t>
+          <t>10 Oct 2026 02:38:29 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:03:45 PM</t>
+          <t>11 Oct 2026 12:07:56 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -9008,39 +10618,39 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 27m</t>
+          <t>21h 29m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1365416</t>
+          <t>TKT1364835</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Mohan Saud</t>
+          <t>Rp.Naan &amp; sekuwa house</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -9050,64 +10660,64 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:03 AM</t>
+          <t>11 Oct 2026 12:03:45 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:03 AM</t>
+          <t>09 Oct 2026 05:36:04 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:15:50 PM</t>
+          <t>11 Oct 2026 12:03:45 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>1d 24m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1d 24m</t>
+          <t>1d 18h 27m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1366330</t>
+          <t>TKT1365416</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Hari Adhikari</t>
+          <t>Mohan Saud</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -9117,44 +10727,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:37 PM</t>
+          <t>10 Oct 2026 11:51:03 AM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:10:11 AM</t>
+          <t>10 Oct 2026 11:51:03 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:37 PM</t>
+          <t>11 Oct 2026 12:15:50 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 24m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1h 36m</t>
+          <t>1d 24m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1365831</t>
+          <t>TKT1366330</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Rajendra magar</t>
+          <t>Hari Adhikari</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -9184,22 +10794,22 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:56 PM</t>
+          <t>11 Oct 2026 12:46:37 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 07:16:39 PM</t>
+          <t>11 Oct 2026 11:10:11 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:56 PM</t>
+          <t>11 Oct 2026 12:46:37 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -9209,39 +10819,39 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>17h 28m</t>
+          <t>1h 36m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1365167</t>
+          <t>TKT1365831</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Niru Gurung</t>
+          <t>Rajendra magar</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -9251,32 +10861,32 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>11 Oct 2026 12:44:56 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>10 Oct 2026 07:16:39 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:21 PM</t>
+          <t>11 Oct 2026 12:44:56 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>17h 28m</t>
         </is>
       </c>
     </row>
@@ -9350,67 +10960,469 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
+          <t>TKT1365167</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Niru Gurung</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:42:24 AM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:46:21 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
           <t>TKT1365633</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Chandra Mani Kharel</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 02:54:06 PM</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 02:54:06 PM</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>11 Oct 2026 12:44:39 PM</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>21h 50m</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>21h 50m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365422</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Thing</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:55:36 AM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:55:36 AM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:08:28 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365422</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Prabin Thing</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:55:36 AM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:55:36 AM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:08:28 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366242</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Joshua Pradhan</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:11:40 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:08:44 AM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:11:40 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>3h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365385</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Sonisha Rijal</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:10:04 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:25:14 AM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:10:04 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358878</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Tanisha giri</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:08:51 PM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:51 AM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:08:51 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>6d 4h 59m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7278,10 +7278,8 @@
           <t>Uttam Kumar Poudel</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9824866858</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9824866858</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7363,10 +7361,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
@@ -7377,7 +7373,7 @@
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7473,10 +7469,8 @@
           <t>Prabin Thing</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9842748830</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9842748830</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7511,10 +7505,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.6889698</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.6889698</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7552,10 +7544,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH36" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH36" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
@@ -7574,25 +7564,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.2921143</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.29211429999999</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7688,10 +7674,8 @@
           <t>Prabin Thing</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9842748830</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9842748830</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7726,10 +7710,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.6889698</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.6889698</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7767,10 +7749,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH37" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH37" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
@@ -7789,25 +7769,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.2921143</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.29211429999999</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -7903,10 +7879,8 @@
           <t>Ashutosh Regmi</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9867171444</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9867171444</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7941,10 +7915,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.70175</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.70175</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -7996,25 +7968,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB091A</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.3341</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.33410000000001</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -8110,10 +8078,8 @@
           <t>Sachit Achhami</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9808426033</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9808426033</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8185,10 +8151,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH39" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH39" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI39" s="3" t="inlineStr"/>
       <c r="AJ39" s="3" t="inlineStr"/>
@@ -8203,10 +8167,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -8217,7 +8179,7 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : no light issue in stb box  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -8313,10 +8275,8 @@
           <t>Joshua Pradhan</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9842749160</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9842749160</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8351,10 +8311,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>27.69337</t>
-        </is>
+      <c r="Y40" s="3" t="n">
+        <v>27.69337</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -8410,25 +8368,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>L28-7</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.34139</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.34139</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8524,10 +8478,8 @@
           <t>Sonisha Rijal</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9858033808</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9858033808</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8562,10 +8514,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.67971</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.67971</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8617,25 +8567,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.33391</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.33391</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8731,10 +8677,8 @@
           <t>Tanisha giri</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9741716174</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9741716174</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8806,10 +8750,8 @@
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH42" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
@@ -8828,10 +8770,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
@@ -8842,7 +8782,7 @@
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -8891,7 +8831,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11124,7 +11064,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -11191,7 +11131,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -11258,7 +11198,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -11325,7 +11265,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -11392,7 +11332,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW42"/>
+  <dimension ref="A1:AW43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,12 +496,12 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8811,6 +8811,217 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 2:13 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : connect disconnect issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>connect disconnect issue</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365618</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Rudra Electronics and Parts</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Rudra Electronics and Parts</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9851144827</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:13:24 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851144827</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:43:27 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:13:24 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>27.700173180185374, 85.2864174821802, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>9851144827@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>05:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr"/>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>CDB016</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : connect disconnect issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>23h 29m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : connect disconnect issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8822,16 +9033,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -8859,7 +9070,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -8869,7 +9080,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -8880,7 +9091,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>73.8%</t>
         </is>
       </c>
     </row>
@@ -8892,7 +9103,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 33m</t>
+          <t>9h 15m</t>
         </is>
       </c>
     </row>
@@ -8904,7 +9115,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 14h 15m</t>
+          <t>1d 13h 46m</t>
         </is>
       </c>
     </row>
@@ -8941,156 +9152,151 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
       <c r="B14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -9108,23 +9314,23 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9342,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -9159,64 +9365,64 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -9228,277 +9434,189 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355718</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Nilam Karki Basnet</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 05:34:53 PM</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364200</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Nipen Shrestha</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 5m</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1364200</t>
+          <t>TKT1355718</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Nipen Shrestha</t>
+          <t>Nilam Karki Basnet</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -9528,22 +9646,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
+          <t>02 Oct 2026 05:34:53 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -9553,29 +9671,29 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1365217</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>yogendra thapa</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -9595,22 +9713,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 09:16:31 AM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -9620,29 +9738,29 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>23h 25m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1364745</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Rajkumar Waiba</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -9662,22 +9780,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:28:55 PM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -9687,29 +9805,29 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 4m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1365217</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>yogendra thapa</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -9729,22 +9847,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : net tv  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>10 Oct 2026 09:16:31 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -9754,29 +9872,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>23h 25m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1364745</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>Rajkumar Waiba</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -9796,22 +9914,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>09 Oct 2026 04:28:55 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -9821,7 +9939,7 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>1d 18h 4m</t>
         </is>
       </c>
     </row>
@@ -9863,7 +9981,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -9895,22 +10013,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1365912</t>
+          <t>TKT1366161</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Sanju Rajya Laxmi Rana</t>
+          <t>Samir Nepal</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -9930,22 +10048,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:47:34 PM</t>
+          <t>11 Oct 2026 09:14:26 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -9955,29 +10073,29 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>14h 58m</t>
+          <t>1h 57m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1364684</t>
+          <t>TKT1366161</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Bhumi Raj Bhandari</t>
+          <t>Samir Nepal</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -9997,22 +10115,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:42:56 PM</t>
+          <t>11 Oct 2026 09:14:26 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -10022,19 +10140,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 45m</t>
+          <t>1h 57m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1359439</t>
+          <t>TKT1365912</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Milan Sijali</t>
+          <t>Sanju Rajya Laxmi Rana</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -10064,22 +10182,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 02:06:45 PM</t>
+          <t>10 Oct 2026 08:47:34 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -10089,19 +10207,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 58m</t>
+          <t>14h 58m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1365285</t>
+          <t>TKT1364684</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Pabita Ale</t>
+          <t>Bhumi Raj Bhandari</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -10131,22 +10249,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:07:56 AM</t>
+          <t>09 Oct 2026 03:42:56 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -10156,19 +10274,19 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 14m</t>
+          <t>1d 19h 45m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1364817</t>
+          <t>TKT1359439</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Indra Bahadur Roka</t>
+          <t>Milan Sijali</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -10183,12 +10301,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -10198,44 +10316,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>05 Oct 2026 02:06:45 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:38:10 AM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>5d 20h 58m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1364817</t>
+          <t>TKT1365285</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Indra Bahadur Roka</t>
+          <t>Pabita Ale</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -10250,12 +10368,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -10265,44 +10383,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : router change  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>10 Oct 2026 10:07:56 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:38:10 AM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>1d 1h 14m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1364249</t>
+          <t>TKT1364817</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Ashish Shrestha</t>
+          <t>Indra Bahadur Roka</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -10332,44 +10450,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:13:46 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:13:46 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:36:50 AM</t>
+          <t>11 Oct 2026 11:38:10 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 23m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 23m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1366209</t>
+          <t>TKT1364817</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Niras Rai</t>
+          <t>Indra Bahadur Roka</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -10384,12 +10502,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -10399,64 +10517,64 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:16:35 PM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:49:43 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:16:35 PM</t>
+          <t>11 Oct 2026 11:38:10 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2h 26m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1366179</t>
+          <t>TKT1364249</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Kristina Chaudhary</t>
+          <t>Ashish Shrestha</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -10466,44 +10584,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:11:12 PM</t>
+          <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:30:28 AM</t>
+          <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:11:12 PM</t>
+          <t>11 Oct 2026 11:36:50 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 1h 23m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>2d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1365609</t>
+          <t>TKT1366209</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Prabin vandari</t>
+          <t>Niras Rai</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -10533,22 +10651,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:07:56 PM</t>
+          <t>11 Oct 2026 12:16:35 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:38:29 PM</t>
+          <t>11 Oct 2026 09:49:43 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:07:56 PM</t>
+          <t>11 Oct 2026 12:16:35 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -10558,29 +10676,29 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>21h 29m</t>
+          <t>2h 26m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1364835</t>
+          <t>TKT1366179</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Rp.Naan &amp; sekuwa house</t>
+          <t>Kristina Chaudhary</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -10600,22 +10718,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:03:45 PM</t>
+          <t>11 Oct 2026 12:11:12 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:36:04 PM</t>
+          <t>11 Oct 2026 09:30:28 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:03:45 PM</t>
+          <t>11 Oct 2026 12:11:12 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -10625,19 +10743,19 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 27m</t>
+          <t>2h 40m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1365416</t>
+          <t>TKT1365609</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Mohan Saud</t>
+          <t>Prabin vandari</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -10652,12 +10770,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -10667,44 +10785,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:03 AM</t>
+          <t>11 Oct 2026 12:07:56 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:03 AM</t>
+          <t>10 Oct 2026 02:38:29 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:15:50 PM</t>
+          <t>11 Oct 2026 12:07:56 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>1d 24m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1d 24m</t>
+          <t>21h 29m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1366330</t>
+          <t>TKT1364835</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Hari Adhikari</t>
+          <t>Rp.Naan &amp; sekuwa house</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -10714,7 +10832,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -10734,22 +10852,22 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:37 PM</t>
+          <t>11 Oct 2026 12:03:45 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:10:11 AM</t>
+          <t>09 Oct 2026 05:36:04 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:37 PM</t>
+          <t>11 Oct 2026 12:03:45 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -10759,39 +10877,39 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>1h 36m</t>
+          <t>1d 18h 27m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1365831</t>
+          <t>TKT1365416</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Rajendra magar</t>
+          <t>Mohan Saud</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -10801,64 +10919,64 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:56 PM</t>
+          <t>10 Oct 2026 11:51:03 AM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 07:16:39 PM</t>
+          <t>10 Oct 2026 11:51:03 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:56 PM</t>
+          <t>11 Oct 2026 12:15:50 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 24m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>17h 28m</t>
+          <t>1d 24m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1365167</t>
+          <t>TKT1366330</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Niru Gurung</t>
+          <t>Hari Adhikari</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -10868,64 +10986,64 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>11 Oct 2026 12:46:37 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>11 Oct 2026 11:10:11 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:21 PM</t>
+          <t>11 Oct 2026 12:46:37 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>1h 36m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1365167</t>
+          <t>TKT1365831</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Niru Gurung</t>
+          <t>Rajendra magar</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -10935,44 +11053,44 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>11 Oct 2026 12:44:56 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>10 Oct 2026 07:16:39 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:21 PM</t>
+          <t>11 Oct 2026 12:44:56 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>17h 28m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1365633</t>
+          <t>TKT1365167</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Chandra Mani Kharel</t>
+          <t>Niru Gurung</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -11002,44 +11120,44 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:54:06 PM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:54:06 PM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:39 PM</t>
+          <t>11 Oct 2026 12:46:21 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>21h 50m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>21h 50m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1365422</t>
+          <t>TKT1365167</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Prabin Thing</t>
+          <t>Niru Gurung</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -11069,44 +11187,44 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:08:28 PM</t>
+          <t>11 Oct 2026 12:46:21 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1365422</t>
+          <t>TKT1365633</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Prabin Thing</t>
+          <t>Chandra Mani Kharel</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -11136,44 +11254,44 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 02:54:06 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 02:54:06 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:08:28 PM</t>
+          <t>11 Oct 2026 12:44:39 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>21h 50m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>21h 50m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1366242</t>
+          <t>TKT1365422</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Joshua Pradhan</t>
+          <t>Prabin Thing</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -11188,12 +11306,12 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -11203,44 +11321,44 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:11:40 PM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:08:44 AM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:11:40 PM</t>
+          <t>11 Oct 2026 01:08:28 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>3h 2m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1365385</t>
+          <t>TKT1365422</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Sonisha Rijal</t>
+          <t>Prabin Thing</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -11255,12 +11373,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -11270,99 +11388,300 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:10:04 PM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:25:14 AM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:10:04 PM</t>
+          <t>11 Oct 2026 01:08:28 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 44m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
+          <t>TKT1366242</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Joshua Pradhan</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:11:40 PM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:08:44 AM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:11:40 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>3h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365385</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Sonisha Rijal</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:10:04 PM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:25:14 AM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:10:04 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
           <t>TKT1358878</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Tanisha giri</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 01:08:51 PM</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>05 Oct 2026 08:09:51 AM</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
+      <c r="K62" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 01:08:51 PM</t>
         </is>
       </c>
-      <c r="L60" s="3" t="inlineStr">
+      <c r="L62" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M60" s="3" t="inlineStr">
+      <c r="M62" s="3" t="inlineStr">
         <is>
           <t>6d 4h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365618</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Rudra Electronics and Parts</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : connect disconnect issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : connect disconnect issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:13:24 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:43:27 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:13:24 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>23h 29m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW43"/>
+  <dimension ref="A1:AW47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -521,7 +521,7 @@
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
@@ -8878,10 +8878,8 @@
           <t>Rudra Electronics and Parts</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9851144827</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9851144827</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8916,10 +8914,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -8975,48 +8971,804 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>CDB016</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>23h 29m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : connect disconnect issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>23h 29m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : connect disconnect issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 2:22 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>5Ghz was not showing</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365640</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Pushpa Bahadur Katuwal</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Pushpa Bahadur Katuwal</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9851160259</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:12:00 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 06: 57:00 PM</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9851160259</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:57:10 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:22:03 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.71085</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Next to Suvarna Store,lakhatirtha marg,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>pushpakatwal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>05:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr">
+        <is>
+          <t>18:57 hour / 00:00 hour</t>
+        </is>
+      </c>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>CDB254</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.30017</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>23h 10m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>23h 24m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 2:21 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>5Ghz was not showing</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365640</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Pushpa Bahadur Katuwal</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Pushpa Bahadur Katuwal</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9851160259</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:12:00 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 06: 57:00 PM</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9851160259</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:57:10 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:22:03 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.71085</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Next to Suvarna Store,lakhatirtha marg,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>pushpakatwal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>05:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr">
+        <is>
+          <t>18:57 hour / 00:00 hour</t>
+        </is>
+      </c>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>CDB254</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.30017</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>23h 10m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>23h 24m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 2:28 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="AA46" s="3" t="inlineStr"/>
+      <c r="AB46" s="3" t="inlineStr"/>
+      <c r="AC46" s="3" t="inlineStr"/>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr"/>
+      <c r="AF46" s="3" t="inlineStr"/>
+      <c r="AG46" s="3" t="inlineStr"/>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr"/>
+      <c r="AM46" s="3" t="inlineStr"/>
+      <c r="AN46" s="3" t="inlineStr"/>
+      <c r="AO46" s="3" t="inlineStr"/>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 2:18 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router still not installed  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>6G router still not installed</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365538</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Sahil Ranjit</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Sahil Ranjit</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9861884278</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:32:08 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9861884278</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:23:42 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:18:58 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.70142</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>New Jashmin Bakery ,Jaisidewal new road, , ,</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>sahil.ranjit1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>06:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr"/>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.30475</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router still not installed  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>1d 46m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>1d 55m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router still not installed  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -9033,7 +9785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9070,7 +9822,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -9080,7 +9832,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -9091,7 +9843,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -9103,7 +9855,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 15m</t>
+          <t>10h 31m</t>
         </is>
       </c>
     </row>
@@ -9115,7 +9867,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 13h 46m</t>
+          <t>1d 12h 33m</t>
         </is>
       </c>
     </row>
@@ -9174,14 +9926,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -9224,136 +9976,131 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
       <c r="B15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Frequent Internet Disconnection</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Due to Configuration Issue</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -9365,18 +10112,18 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -9388,18 +10135,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -9411,7 +10158,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -9429,23 +10176,23 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -9457,18 +10204,18 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -9480,277 +10227,189 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr"/>
-      <c r="B29" s="5" t="inlineStr"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
       <c r="C29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355718</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Nilam Karki Basnet</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 05:34:53 PM</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364200</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Nipen Shrestha</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 5m</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1364200</t>
+          <t>TKT1355718</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Nipen Shrestha</t>
+          <t>Nilam Karki Basnet</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -9780,22 +10439,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
+          <t>02 Oct 2026 05:34:53 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -9805,29 +10464,29 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1365217</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>yogendra thapa</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -9847,22 +10506,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 09:16:31 AM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -9872,29 +10531,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>23h 25m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1364745</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Rajkumar Waiba</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -9914,22 +10573,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:28:55 PM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -9939,29 +10598,29 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 4m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1365217</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>yogendra thapa</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -9981,22 +10640,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : net tv  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>10 Oct 2026 09:16:31 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -10006,29 +10665,29 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>23h 25m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1364745</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>Rajkumar Waiba</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -10048,22 +10707,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>09 Oct 2026 04:28:55 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -10073,7 +10732,7 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>1d 18h 4m</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10774,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -10147,22 +10806,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1365912</t>
+          <t>TKT1366161</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Sanju Rajya Laxmi Rana</t>
+          <t>Samir Nepal</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -10182,22 +10841,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:47:34 PM</t>
+          <t>11 Oct 2026 09:14:26 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -10207,29 +10866,29 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>14h 58m</t>
+          <t>1h 57m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1364684</t>
+          <t>TKT1366161</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Bhumi Raj Bhandari</t>
+          <t>Samir Nepal</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -10249,22 +10908,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:42:56 PM</t>
+          <t>11 Oct 2026 09:14:26 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -10274,19 +10933,19 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 45m</t>
+          <t>1h 57m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1359439</t>
+          <t>TKT1365912</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Milan Sijali</t>
+          <t>Sanju Rajya Laxmi Rana</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -10316,22 +10975,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 02:06:45 PM</t>
+          <t>10 Oct 2026 08:47:34 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -10341,19 +11000,19 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 58m</t>
+          <t>14h 58m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1365285</t>
+          <t>TKT1364684</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Pabita Ale</t>
+          <t>Bhumi Raj Bhandari</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -10383,22 +11042,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:07:56 AM</t>
+          <t>09 Oct 2026 03:42:56 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -10408,19 +11067,19 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 14m</t>
+          <t>1d 19h 45m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1364817</t>
+          <t>TKT1359439</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Indra Bahadur Roka</t>
+          <t>Milan Sijali</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -10435,12 +11094,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -10450,44 +11109,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>05 Oct 2026 02:06:45 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:38:10 AM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>5d 20h 58m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1364817</t>
+          <t>TKT1365285</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Indra Bahadur Roka</t>
+          <t>Pabita Ale</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -10502,12 +11161,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -10517,44 +11176,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : router change  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>10 Oct 2026 10:07:56 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:38:10 AM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>1d 1h 14m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1364249</t>
+          <t>TKT1364817</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Ashish Shrestha</t>
+          <t>Indra Bahadur Roka</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -10584,44 +11243,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:13:46 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:13:46 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:36:50 AM</t>
+          <t>11 Oct 2026 11:38:10 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 23m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 23m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1366209</t>
+          <t>TKT1364817</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Niras Rai</t>
+          <t>Indra Bahadur Roka</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -10636,12 +11295,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -10651,64 +11310,64 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:16:35 PM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:49:43 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:16:35 PM</t>
+          <t>11 Oct 2026 11:38:10 AM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>2h 26m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1366179</t>
+          <t>TKT1364249</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Kristina Chaudhary</t>
+          <t>Ashish Shrestha</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -10718,44 +11377,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:11:12 PM</t>
+          <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:30:28 AM</t>
+          <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:11:12 PM</t>
+          <t>11 Oct 2026 11:36:50 AM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 1h 23m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>2d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1365609</t>
+          <t>TKT1366209</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Prabin vandari</t>
+          <t>Niras Rai</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -10785,22 +11444,22 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:07:56 PM</t>
+          <t>11 Oct 2026 12:16:35 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:38:29 PM</t>
+          <t>11 Oct 2026 09:49:43 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:07:56 PM</t>
+          <t>11 Oct 2026 12:16:35 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -10810,29 +11469,29 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>21h 29m</t>
+          <t>2h 26m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1364835</t>
+          <t>TKT1366179</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Rp.Naan &amp; sekuwa house</t>
+          <t>Kristina Chaudhary</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -10852,22 +11511,22 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:03:45 PM</t>
+          <t>11 Oct 2026 12:11:12 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:36:04 PM</t>
+          <t>11 Oct 2026 09:30:28 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:03:45 PM</t>
+          <t>11 Oct 2026 12:11:12 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -10877,19 +11536,19 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 27m</t>
+          <t>2h 40m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1365416</t>
+          <t>TKT1365609</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Mohan Saud</t>
+          <t>Prabin vandari</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -10904,12 +11563,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -10919,44 +11578,44 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:03 AM</t>
+          <t>11 Oct 2026 12:07:56 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:03 AM</t>
+          <t>10 Oct 2026 02:38:29 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:15:50 PM</t>
+          <t>11 Oct 2026 12:07:56 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>1d 24m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1d 24m</t>
+          <t>21h 29m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1366330</t>
+          <t>TKT1364835</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Hari Adhikari</t>
+          <t>Rp.Naan &amp; sekuwa house</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -10966,7 +11625,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -10986,22 +11645,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:37 PM</t>
+          <t>11 Oct 2026 12:03:45 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:10:11 AM</t>
+          <t>09 Oct 2026 05:36:04 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:37 PM</t>
+          <t>11 Oct 2026 12:03:45 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -11011,39 +11670,39 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>1h 36m</t>
+          <t>1d 18h 27m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1365831</t>
+          <t>TKT1365416</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Rajendra magar</t>
+          <t>Mohan Saud</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -11053,64 +11712,64 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:56 PM</t>
+          <t>10 Oct 2026 11:51:03 AM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 07:16:39 PM</t>
+          <t>10 Oct 2026 11:51:03 AM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:56 PM</t>
+          <t>11 Oct 2026 12:15:50 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 24m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>17h 28m</t>
+          <t>1d 24m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1365167</t>
+          <t>TKT1366330</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Niru Gurung</t>
+          <t>Hari Adhikari</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -11120,64 +11779,64 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>11 Oct 2026 12:46:37 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>11 Oct 2026 11:10:11 AM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:21 PM</t>
+          <t>11 Oct 2026 12:46:37 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>1h 36m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1365167</t>
+          <t>TKT1365831</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Niru Gurung</t>
+          <t>Rajendra magar</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -11187,44 +11846,44 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>11 Oct 2026 12:44:56 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>10 Oct 2026 07:16:39 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:21 PM</t>
+          <t>11 Oct 2026 12:44:56 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>17h 28m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1365633</t>
+          <t>TKT1365167</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Chandra Mani Kharel</t>
+          <t>Niru Gurung</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -11254,44 +11913,44 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:54:06 PM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:54:06 PM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:39 PM</t>
+          <t>11 Oct 2026 12:46:21 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>21h 50m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>21h 50m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1365422</t>
+          <t>TKT1365167</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Prabin Thing</t>
+          <t>Niru Gurung</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -11321,44 +11980,44 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:08:28 PM</t>
+          <t>11 Oct 2026 12:46:21 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1365422</t>
+          <t>TKT1365633</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Prabin Thing</t>
+          <t>Chandra Mani Kharel</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -11388,44 +12047,44 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 02:54:06 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 02:54:06 PM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:08:28 PM</t>
+          <t>11 Oct 2026 12:44:39 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>21h 50m</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>21h 50m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1366242</t>
+          <t>TKT1365422</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Joshua Pradhan</t>
+          <t>Prabin Thing</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -11440,12 +12099,12 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -11455,44 +12114,44 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:11:40 PM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:08:44 AM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:11:40 PM</t>
+          <t>11 Oct 2026 01:08:28 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>3h 2m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1365385</t>
+          <t>TKT1365422</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Sonisha Rijal</t>
+          <t>Prabin Thing</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -11507,12 +12166,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -11522,54 +12181,54 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:10:04 PM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:25:14 AM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:10:04 PM</t>
+          <t>11 Oct 2026 01:08:28 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 44m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1358878</t>
+          <t>TKT1366242</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Tanisha giri</t>
+          <t>Joshua Pradhan</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -11589,22 +12248,22 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:08:51 PM</t>
+          <t>11 Oct 2026 01:11:40 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:09:51 AM</t>
+          <t>11 Oct 2026 10:08:44 AM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:08:51 PM</t>
+          <t>11 Oct 2026 01:11:40 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -11614,74 +12273,409 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>6d 4h 59m</t>
+          <t>3h 2m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
+          <t>TKT1365385</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Sonisha Rijal</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:10:04 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:25:14 AM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:10:04 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358878</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Tanisha giri</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:08:51 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:51 AM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:08:51 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>6d 4h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
           <t>TKT1365618</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Rudra Electronics and Parts</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Frequent Internet Disconnection</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Due to Configuration Issue</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>Case : connect disconnect issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>Case : connect disconnect issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>11 Oct 2026 02:13:24 PM</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 02:43:27 PM</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>11 Oct 2026 02:13:24 PM</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr">
+      <c r="L65" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="M65" s="5" t="inlineStr">
         <is>
           <t>23h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365640</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Pushpa Bahadur Katuwal</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:12:00 PM</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:57:10 PM</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:22:03 PM</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>23h 10m</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>23h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365640</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Pushpa Bahadur Katuwal</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:12:00 PM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:57:10 PM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:22:03 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>23h 10m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>23h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365538</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Sahil Ranjit</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router still not installed  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router still not installed  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:32:08 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:23:42 PM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:18:58 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>1d 46m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>1d 55m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW47"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9081,10 +9081,8 @@
           <t>Pushpa Bahadur Katuwal</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9851160259</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9851160259</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9123,10 +9121,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>27.71085</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>27.71085</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -9164,10 +9160,8 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH44" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH44" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
@@ -9190,25 +9184,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>CDB254</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.30017</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.30016999999999</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9304,10 +9294,8 @@
           <t>Pushpa Bahadur Katuwal</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9851160259</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9851160259</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9346,10 +9334,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.71085</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.71085</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9387,10 +9373,8 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH45" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH45" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
@@ -9413,25 +9397,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>CDB254</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.30017</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.30016999999999</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -9630,10 +9610,8 @@
           <t>Sahil Ranjit</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9861884278</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9861884278</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9668,10 +9646,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.70142</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.70142</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -9727,48 +9703,255 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.30475</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.30475</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>1d 46m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>1d 55m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
           <t>Case : 6G router still not installed  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS47" s="3" t="inlineStr">
-        <is>
-          <t>1d 46m</t>
-        </is>
-      </c>
-      <c r="AT47" s="3" t="inlineStr">
-        <is>
-          <t>1d 55m</t>
-        </is>
-      </c>
-      <c r="AU47" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV47" s="3" t="inlineStr">
-        <is>
-          <t>Case : 6G router still not installed  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 2:43 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : net slow  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>net slow</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364785</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Hotel blue star</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Hotel blue star</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9849155008</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:43:53 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>KLK9849155008</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:50:08 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:43:53 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>1@g.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>13:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Nitesh Thakur</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>L47-7A</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : net slow  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 53m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : net slow  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -9785,13 +9968,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -9822,7 +10005,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -9832,7 +10015,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -9843,7 +10026,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>74.5%</t>
         </is>
       </c>
     </row>
@@ -9855,7 +10038,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 31m</t>
+          <t>10h 13m</t>
         </is>
       </c>
     </row>
@@ -9867,7 +10050,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 12h 33m</t>
+          <t>1d 12h 49m</t>
         </is>
       </c>
     </row>
@@ -9994,136 +10177,131 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
       <c r="B16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Frequent Internet Disconnection</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Due to Configuration Issue</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -10135,18 +10313,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -10158,18 +10336,18 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10359,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -10199,23 +10377,23 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -10227,18 +10405,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -10250,37 +10428,37 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -10291,259 +10469,171 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr"/>
-      <c r="B31" s="5" t="inlineStr"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
       <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355718</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Nilam Karki Basnet</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 05:34:53 PM</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:59:43 AM</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364200</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Nipen Shrestha</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 5m</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1364200</t>
+          <t>TKT1355718</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Nipen Shrestha</t>
+          <t>Nilam Karki Basnet</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -10573,22 +10663,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:52:25 AM</t>
+          <t>02 Oct 2026 05:34:53 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 07:58:19 AM</t>
+          <t>11 Oct 2026 07:59:43 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -10598,29 +10688,29 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 5m</t>
+          <t>8d 14h 24m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1365217</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>yogendra thapa</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -10640,22 +10730,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 09:16:31 AM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 08:42:10 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -10665,29 +10755,29 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>23h 25m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1364745</t>
+          <t>TKT1364200</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Rajkumar Waiba</t>
+          <t>Nipen Shrestha</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -10707,22 +10797,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:28:55 PM</t>
+          <t>09 Oct 2026 09:52:25 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:33:28 AM</t>
+          <t>11 Oct 2026 07:58:19 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -10732,29 +10822,29 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 4m</t>
+          <t>1d 22h 5m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1365217</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>yogendra thapa</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -10774,22 +10864,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : net tv  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>10 Oct 2026 09:16:31 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 08:42:10 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -10799,29 +10889,29 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>23h 25m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1366161</t>
+          <t>TKT1364745</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Samir Nepal</t>
+          <t>Rajkumar Waiba</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-STB App not working</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -10841,22 +10931,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+          <t>Case : red light issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:14:26 AM</t>
+          <t>09 Oct 2026 04:28:55 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:11:41 AM</t>
+          <t>11 Oct 2026 10:33:28 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -10866,7 +10956,7 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>1h 57m</t>
+          <t>1d 18h 4m</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10998,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : net tv  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -10940,22 +11030,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1365912</t>
+          <t>TKT1366161</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Sanju Rajya Laxmi Rana</t>
+          <t>Samir Nepal</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -10975,22 +11065,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:47:34 PM</t>
+          <t>11 Oct 2026 09:14:26 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:46:03 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -11000,29 +11090,29 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>14h 58m</t>
+          <t>1h 57m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1364684</t>
+          <t>TKT1366161</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Bhumi Raj Bhandari</t>
+          <t>Samir Nepal</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-STB App not working</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -11042,22 +11132,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:42:56 PM</t>
+          <t>11 Oct 2026 09:14:26 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:28:28 AM</t>
+          <t>11 Oct 2026 11:11:41 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -11067,19 +11157,19 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 45m</t>
+          <t>1h 57m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1359439</t>
+          <t>TKT1365912</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Milan Sijali</t>
+          <t>Sanju Rajya Laxmi Rana</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -11109,22 +11199,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 02:06:45 PM</t>
+          <t>10 Oct 2026 08:47:34 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:04:49 AM</t>
+          <t>11 Oct 2026 11:46:03 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -11134,19 +11224,19 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 58m</t>
+          <t>14h 58m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1365285</t>
+          <t>TKT1364684</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Pabita Ale</t>
+          <t>Bhumi Raj Bhandari</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -11176,22 +11266,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : router change  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:07:56 AM</t>
+          <t>09 Oct 2026 03:42:56 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:22:40 AM</t>
+          <t>11 Oct 2026 11:28:28 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -11201,19 +11291,19 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 14m</t>
+          <t>1d 19h 45m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1364817</t>
+          <t>TKT1359439</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Indra Bahadur Roka</t>
+          <t>Milan Sijali</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -11228,12 +11318,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -11243,44 +11333,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>05 Oct 2026 02:06:45 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:38:10 AM</t>
+          <t>11 Oct 2026 11:04:49 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>5d 20h 58m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1364817</t>
+          <t>TKT1365285</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Indra Bahadur Roka</t>
+          <t>Pabita Ale</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -11295,12 +11385,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -11310,44 +11400,44 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : router change  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:19:02 PM</t>
+          <t>10 Oct 2026 10:07:56 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:38:10 AM</t>
+          <t>11 Oct 2026 11:22:40 AM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 19m</t>
+          <t>1d 1h 14m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1364249</t>
+          <t>TKT1364817</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Ashish Shrestha</t>
+          <t>Indra Bahadur Roka</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -11377,44 +11467,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:13:46 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:13:46 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:36:50 AM</t>
+          <t>11 Oct 2026 11:38:10 AM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 23m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 23m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1366209</t>
+          <t>TKT1364817</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Niras Rai</t>
+          <t>Indra Bahadur Roka</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -11429,12 +11519,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -11444,64 +11534,64 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:16:35 PM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:49:43 AM</t>
+          <t>09 Oct 2026 05:19:02 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:16:35 PM</t>
+          <t>11 Oct 2026 11:38:10 AM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>2h 26m</t>
+          <t>1d 18h 19m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1366179</t>
+          <t>TKT1364249</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Kristina Chaudhary</t>
+          <t>Ashish Shrestha</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -11511,44 +11601,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:11:12 PM</t>
+          <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 09:30:28 AM</t>
+          <t>09 Oct 2026 10:13:46 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:11:12 PM</t>
+          <t>11 Oct 2026 11:36:50 AM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 1h 23m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>2d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1365609</t>
+          <t>TKT1366209</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Prabin vandari</t>
+          <t>Niras Rai</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -11578,22 +11668,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:07:56 PM</t>
+          <t>11 Oct 2026 12:16:35 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:38:29 PM</t>
+          <t>11 Oct 2026 09:49:43 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:07:56 PM</t>
+          <t>11 Oct 2026 12:16:35 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -11603,29 +11693,29 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>21h 29m</t>
+          <t>2h 26m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1364835</t>
+          <t>TKT1366179</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Rp.Naan &amp; sekuwa house</t>
+          <t>Kristina Chaudhary</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -11645,22 +11735,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:03:45 PM</t>
+          <t>11 Oct 2026 12:11:12 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:36:04 PM</t>
+          <t>11 Oct 2026 09:30:28 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:03:45 PM</t>
+          <t>11 Oct 2026 12:11:12 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -11670,19 +11760,19 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>1d 18h 27m</t>
+          <t>2h 40m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1365416</t>
+          <t>TKT1365609</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Mohan Saud</t>
+          <t>Prabin vandari</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -11697,12 +11787,12 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -11712,44 +11802,44 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:03 AM</t>
+          <t>11 Oct 2026 12:07:56 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:03 AM</t>
+          <t>10 Oct 2026 02:38:29 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:15:50 PM</t>
+          <t>11 Oct 2026 12:07:56 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>1d 24m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1d 24m</t>
+          <t>21h 29m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1366330</t>
+          <t>TKT1364835</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Hari Adhikari</t>
+          <t>Rp.Naan &amp; sekuwa house</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -11759,7 +11849,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -11779,22 +11869,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
+          <t>Case : router  replaced  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:37 PM</t>
+          <t>11 Oct 2026 12:03:45 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 11:10:11 AM</t>
+          <t>09 Oct 2026 05:36:04 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:37 PM</t>
+          <t>11 Oct 2026 12:03:45 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -11804,39 +11894,39 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>1h 36m</t>
+          <t>1d 18h 27m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1365831</t>
+          <t>TKT1365416</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Rajendra magar</t>
+          <t>Mohan Saud</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -11846,64 +11936,64 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:56 PM</t>
+          <t>10 Oct 2026 11:51:03 AM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 07:16:39 PM</t>
+          <t>10 Oct 2026 11:51:03 AM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:56 PM</t>
+          <t>11 Oct 2026 12:15:50 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 24m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>17h 28m</t>
+          <t>1d 24m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1365167</t>
+          <t>TKT1366330</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Niru Gurung</t>
+          <t>Hari Adhikari</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -11913,64 +12003,64 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : STB red light issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>11 Oct 2026 12:46:37 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>11 Oct 2026 11:10:11 AM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:21 PM</t>
+          <t>11 Oct 2026 12:46:37 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>1h 36m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1365167</t>
+          <t>TKT1365831</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Niru Gurung</t>
+          <t>Rajendra magar</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -11980,44 +12070,44 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>11 Oct 2026 12:44:56 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:42:24 AM</t>
+          <t>10 Oct 2026 07:16:39 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:46:21 PM</t>
+          <t>11 Oct 2026 12:44:56 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 3m</t>
+          <t>17h 28m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1365633</t>
+          <t>TKT1365167</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Chandra Mani Kharel</t>
+          <t>Niru Gurung</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -12047,44 +12137,44 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:54:06 PM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:54:06 PM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 12:44:39 PM</t>
+          <t>11 Oct 2026 12:46:21 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>21h 50m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>21h 50m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1365422</t>
+          <t>TKT1365167</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Prabin Thing</t>
+          <t>Niru Gurung</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -12114,44 +12204,44 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 08:42:24 AM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:08:28 PM</t>
+          <t>11 Oct 2026 12:46:21 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>1d 4h 3m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1365422</t>
+          <t>TKT1365633</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Prabin Thing</t>
+          <t>Chandra Mani Kharel</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -12181,44 +12271,44 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 02:54:06 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:55:36 AM</t>
+          <t>10 Oct 2026 02:54:06 PM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:08:28 PM</t>
+          <t>11 Oct 2026 12:44:39 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>21h 50m</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 12m</t>
+          <t>21h 50m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1366242</t>
+          <t>TKT1365422</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Joshua Pradhan</t>
+          <t>Prabin Thing</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12233,12 +12323,12 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -12248,44 +12338,44 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:11:40 PM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 10:08:44 AM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:11:40 PM</t>
+          <t>11 Oct 2026 01:08:28 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>3h 2m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1365385</t>
+          <t>TKT1365422</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Sonisha Rijal</t>
+          <t>Prabin Thing</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -12300,12 +12390,12 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -12315,54 +12405,54 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:10:04 PM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:25:14 AM</t>
+          <t>10 Oct 2026 11:55:36 AM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:10:04 PM</t>
+          <t>11 Oct 2026 01:08:28 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 44m</t>
+          <t>1d 1h 12m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>TKT1358878</t>
+          <t>TKT1366242</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Tanisha giri</t>
+          <t>Joshua Pradhan</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -12382,22 +12472,22 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:08:51 PM</t>
+          <t>11 Oct 2026 01:11:40 PM</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:09:51 AM</t>
+          <t>11 Oct 2026 10:08:44 AM</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 01:08:51 PM</t>
+          <t>11 Oct 2026 01:11:40 PM</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -12407,29 +12497,29 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>6d 4h 59m</t>
+          <t>3h 2m</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TKT1365618</t>
+          <t>TKT1365385</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Rudra Electronics and Parts</t>
+          <t>Sonisha Rijal</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -12449,22 +12539,22 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Case : connect disconnect issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 02:13:24 PM</t>
+          <t>11 Oct 2026 01:10:04 PM</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:43:27 PM</t>
+          <t>10 Oct 2026 11:25:14 AM</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 02:13:24 PM</t>
+          <t>11 Oct 2026 01:10:04 PM</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
@@ -12474,208 +12564,409 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>23h 29m</t>
+          <t>1d 1h 44m</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>TKT1365640</t>
+          <t>TKT1358878</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Pushpa Bahadur Katuwal</t>
+          <t>Tanisha giri</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:12:00 PM</t>
+          <t>11 Oct 2026 01:08:51 PM</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:57:10 PM</t>
+          <t>05 Oct 2026 08:09:51 AM</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>11 Oct 2026 02:22:03 PM</t>
+          <t>11 Oct 2026 01:08:51 PM</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>23h 10m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>23h 24m</t>
+          <t>6d 4h 59m</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TKT1365640</t>
+          <t>TKT1365618</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Pushpa Bahadur Katuwal</t>
+          <t>Rudra Electronics and Parts</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+          <t>Case : connect disconnect issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:12:00 PM</t>
+          <t>11 Oct 2026 02:13:24 PM</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:57:10 PM</t>
+          <t>10 Oct 2026 02:43:27 PM</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 2026 02:22:03 PM</t>
+          <t>11 Oct 2026 02:13:24 PM</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>23h 10m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>23h 24m</t>
+          <t>23h 29m</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
+          <t>TKT1365640</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Pushpa Bahadur Katuwal</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:12:00 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:57:10 PM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:22:03 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>23h 10m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>23h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365640</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Pushpa Bahadur Katuwal</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Case : 5Ghz was not showing   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:12:00 PM</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:57:10 PM</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:22:03 PM</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>23h 10m</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>23h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
           <t>TKT1365538</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Sahil Ranjit</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>Case : 6G router still not installed  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>Case : 6G router still not installed  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 01:32:08 PM</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 01:23:42 PM</t>
         </is>
       </c>
-      <c r="K68" s="3" t="inlineStr">
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 02:18:58 PM</t>
         </is>
       </c>
-      <c r="L68" s="3" t="inlineStr">
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>1d 46m</t>
         </is>
       </c>
-      <c r="M68" s="3" t="inlineStr">
+      <c r="M70" s="3" t="inlineStr">
         <is>
           <t>1d 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364785</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Hotel blue star</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Case : net slow  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : net slow  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:43:53 PM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:50:08 PM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:43:53 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>1d 21h 53m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9813,10 +9813,8 @@
           <t>Hotel blue star</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9849155008</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9849155008</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9851,10 +9849,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -9910,25 +9906,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>L47-7A</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : net slow  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
@@ -9977,7 +9969,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -12936,7 +12928,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Case : net slow  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9949,6 +9949,209 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 3:12 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>range issue</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364159</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Aarati Malla Thakuri</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Aarati Malla Thakuri</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9849257495</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 11:19:34 AM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9849257495</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:29:42 AM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:12:53 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.66091</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Imadol, Mahalaxmi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr"/>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr"/>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>4,6</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.347773</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 53m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 43m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9997,7 +10200,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -10018,7 +10221,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>72.9%</t>
         </is>
       </c>
     </row>
@@ -10191,7 +10394,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
@@ -10516,7 +10719,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>0</v>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW49"/>
+  <dimension ref="A1:AW51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -10016,10 +10016,8 @@
           <t>Aarati Malla Thakuri</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9849257495</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9849257495</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10054,10 +10052,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.66091</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.66091</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -10105,50 +10101,456 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>4,6</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.347773</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.347773</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 53m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 43m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
           <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS49" s="3" t="inlineStr">
-        <is>
-          <t>2d 3h 53m</t>
-        </is>
-      </c>
-      <c r="AT49" s="3" t="inlineStr">
-        <is>
-          <t>2d 5h 43m</t>
-        </is>
-      </c>
-      <c r="AU49" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV49" s="3" t="inlineStr">
-        <is>
-          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW49" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 3:17 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>STB faulty</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365343</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Lal Shrestha</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Lal Shrestha</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9861837436</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:17:34 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>CHB9861837436</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:49:43 AM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:17:34 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr"/>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>27.72187828332493, 85.30764362100628, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>9861837436@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>09:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr"/>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 27m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 3:24 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366549</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9860577686</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:24:40 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9841728074</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:28:33 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:24:40 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.73023</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Tushal Multivenue - Event venue Tushal 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>adhikarihrithik2022@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr"/>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L55-4</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.3151</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>1h 56m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -10163,7 +10565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10172,7 +10574,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10200,7 +10602,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -10210,7 +10612,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -10221,7 +10623,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -10233,7 +10635,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 13m</t>
+          <t>9h 56m</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10647,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 12h 49m</t>
+          <t>1d 12h 35m</t>
         </is>
       </c>
     </row>
@@ -10304,14 +10706,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -10322,14 +10724,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -10489,14 +10891,14 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>21</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -10535,14 +10937,14 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -13165,6 +13567,73 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365343</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Lal Shrestha</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:17:34 PM</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:49:43 AM</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:17:34 PM</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 27m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW51"/>
+  <dimension ref="A1:AW53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10211,10 +10211,8 @@
           <t>Dinesh Lal Shrestha</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9861837436</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9861837436</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10304,10 +10302,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
@@ -10318,7 +10314,7 @@
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : STB faulty   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -10414,10 +10410,8 @@
           <t>Janak Adhikari</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9860577686</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9860577686</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10452,10 +10446,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.73023</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.73023</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -10507,50 +10499,460 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>L55-4</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.3151</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.3151</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>1h 56m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS51" s="3" t="inlineStr">
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 3:43 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>range issue</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364159</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Aarati Malla Thakuri</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Aarati Malla Thakuri</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9849257495</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:43:26 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9849257495</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:29:42 AM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:43:26 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.66091</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Imadol, Mahalaxmi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr"/>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>20:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>4,6</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.347773</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>1h 56m</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV51" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW51" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 13m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 3:42 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>router damage</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366541</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Sujit Giri</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Sujit Giri</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9827436689</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:42:45 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9827436689</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:26:24 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:42:45 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.70245</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>???? ?????? ?????? - Hindu temple M9WH+JW7 Kageshwori Manohara 44600, , ,</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr"/>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>L55-7</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.383943</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>2h 16m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10602,7 +11004,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -10612,7 +11014,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -10623,7 +11025,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -10635,7 +11037,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 56m</t>
+          <t>9h 25m</t>
         </is>
       </c>
     </row>
@@ -10647,7 +11049,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 12h 35m</t>
+          <t>1d 12h 9m</t>
         </is>
       </c>
     </row>
@@ -10724,14 +11126,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -10796,14 +11198,14 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -10983,10 +11385,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -11121,14 +11523,14 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -13600,14 +14002,14 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
           <t>Case : STB faulty   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>Case : STB faulty   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 03:17:34 PM</t>
@@ -13631,6 +14033,140 @@
       <c r="M72" s="3" t="inlineStr">
         <is>
           <t>1d 4h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364159</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Aarati Malla Thakuri</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:43:26 PM</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:29:42 AM</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:43:26 PM</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>2d 6h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366541</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Sujit Giri</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:42:45 PM</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:26:24 PM</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:42:45 PM</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>2h 16m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW53"/>
+  <dimension ref="A1:AW54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10609,10 +10609,8 @@
           <t>Aarati Malla Thakuri</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9849257495</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9849257495</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10647,10 +10645,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.66091</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.66091</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10702,25 +10698,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>4,6</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.347773</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.347773</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -10816,10 +10808,8 @@
           <t>Sujit Giri</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9827436689</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9827436689</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -10854,10 +10844,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.70245</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.70245</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -10909,50 +10897,257 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>L55-7</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.383943</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.383943</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>2h 16m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
           <t>Case : router damage  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS53" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT53" s="3" t="inlineStr">
-        <is>
-          <t>2h 16m</t>
-        </is>
-      </c>
-      <c r="AU53" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV53" s="3" t="inlineStr">
-        <is>
-          <t>Case : router damage  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 3:50 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365588</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Reenu Pujari</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Reenu Pujari</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9841051286</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:23:32 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9841051286</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:23:32 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:50:43 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>27.71131</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Dallu, Dhalku -17, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>reenupujari143@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>05:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>85.30467</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 27m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 27m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -10967,7 +11162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11004,7 +11199,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -11014,7 +11209,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -11025,7 +11220,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>73.6%</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11232,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 25m</t>
+          <t>9h 49m</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11244,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 12h 9m</t>
+          <t>1d 11h 52m</t>
         </is>
       </c>
     </row>
@@ -11108,14 +11303,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -11293,14 +11488,14 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -14069,7 +14264,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Case : range issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -14136,14 +14331,14 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
           <t>Case : router damage  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>Case : router damage  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026 03:42:45 PM</t>
@@ -14167,6 +14362,73 @@
       <c r="M74" s="3" t="inlineStr">
         <is>
           <t>2h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365588</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Reenu Pujari</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:23:32 PM</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:23:32 PM</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:50:43 PM</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 27m</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 27m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11007,10 +11007,8 @@
           <t>Reenu Pujari</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9841051286</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9841051286</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -11045,10 +11043,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y54" s="3" t="inlineStr">
-        <is>
-          <t>27.71131</t>
-        </is>
+      <c r="Y54" s="3" t="n">
+        <v>27.71131</v>
       </c>
       <c r="Z54" s="3" t="inlineStr">
         <is>
@@ -11104,25 +11100,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>85.30467</t>
-        </is>
+      <c r="AP54" s="3" t="n">
+        <v>85.30467</v>
       </c>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -11171,7 +11163,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -14398,7 +14390,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW54"/>
+  <dimension ref="A1:AW55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11143,6 +11143,217 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 4:28 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366184</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Aarya Timalsina</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Aarya Timalsina</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9846663888</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:28:54 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9843820875</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:32:14 AM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:28:54 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.68154</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Swapna Vatika SchoolM8MH+RP6, Kathmandu 44600., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>aaryasinna@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.33094</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>6h 56m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11154,7 +11365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11163,7 +11374,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11191,7 +11402,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -11201,7 +11412,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -11212,7 +11423,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -11224,7 +11435,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 49m</t>
+          <t>9h 35m</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11447,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 11h 52m</t>
+          <t>1d 11h 9m</t>
         </is>
       </c>
     </row>
@@ -11295,14 +11506,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -11480,14 +11691,14 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -14424,6 +14635,73 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366184</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Aarya Timalsina</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:28:54 PM</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:32:14 AM</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:28:54 PM</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>6h 56m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_11_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_11_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11210,10 +11210,8 @@
           <t>Aarya Timalsina</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9846663888</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9846663888</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -11248,10 +11246,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.68154</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.68154</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -11307,25 +11303,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.33094</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.33094</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -11374,7 +11366,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -14668,7 +14660,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
